--- a/database/controller_excel/FO-DSP-TI-02 Reporte de auditoria a herramientas TI Rev.00.xlsx
+++ b/database/controller_excel/FO-DSP-TI-02 Reporte de auditoria a herramientas TI Rev.00.xlsx
@@ -1,12 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Inventario_TI\database\controller_excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Reporte Auditoria" sheetId="1" r:id="rId4"/>
+    <sheet name="Reporte Auditoria" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -63,18 +71,19 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <b/>
-        <color rgb="FFFFFFFF"/>
       </rPr>
       <t xml:space="preserve">OBSERVACIONES:
 </t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <b val="0"/>
-        <color rgb="FFFFFFFF"/>
       </rPr>
       <t>Reportar las fallas que presenta el equipo regularmente y las anomalías detectadas durante la auditoría</t>
     </r>
@@ -128,60 +137,98 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="11">
-    <font>
-      <sz val="10.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="15" x14ac:knownFonts="1">
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -189,7 +236,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -204,12 +251,22 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
-    <border/>
-    <border>
+  <borders count="18">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -218,27 +275,40 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -253,32 +323,47 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-    </border>
-    <border>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -287,22 +372,27 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -312,6 +402,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -323,135 +414,200 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="14" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="56">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -462,11 +618,11 @@
     <xdr:ext cx="714375" cy="752475"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Imagen"/>
+        <xdr:cNvPr id="2" name="image1.png" title="Imagen"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -484,7 +640,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -674,29 +830,32 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:O39"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="4.25"/>
-    <col customWidth="1" min="2" max="2" width="14.0"/>
-    <col customWidth="1" min="3" max="3" width="12.63"/>
-    <col customWidth="1" min="4" max="4" width="15.13"/>
-    <col customWidth="1" min="5" max="6" width="18.88"/>
-    <col customWidth="1" min="7" max="8" width="12.63"/>
-    <col customWidth="1" min="9" max="9" width="15.13"/>
-    <col customWidth="1" min="11" max="11" width="48.38"/>
-    <col customWidth="1" min="12" max="12" width="5.25"/>
+    <col min="1" max="1" width="4.21875" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" customWidth="1"/>
+    <col min="5" max="6" width="18.88671875" customWidth="1"/>
+    <col min="7" max="8" width="12.6640625" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" customWidth="1"/>
+    <col min="11" max="11" width="48.33203125" customWidth="1"/>
+    <col min="12" max="12" width="5.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -706,69 +865,82 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="8" t="s">
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="10"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="12" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="12" t="s">
+      <c r="B4" s="29"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="16" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="11"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="25"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="15"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
+      <c r="B6" s="30"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="37"/>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -778,23 +950,23 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="J8" s="18" t="s">
+      <c r="C8" s="39"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="J8" s="6" t="s">
         <v>6</v>
       </c>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -804,24 +976,24 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="14"/>
-      <c r="F10" s="18" t="s">
+      <c r="C10" s="39"/>
+      <c r="D10" s="36"/>
+      <c r="F10" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="14"/>
-      <c r="J10" s="18" t="s">
+      <c r="G10" s="39"/>
+      <c r="H10" s="36"/>
+      <c r="J10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="19"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
+      <c r="K10" s="7"/>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -831,7 +1003,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -841,294 +1013,290 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:15" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="22" t="s">
+      <c r="F13" s="25"/>
+      <c r="G13" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="15"/>
-      <c r="I13" s="23" t="s">
+      <c r="H13" s="25"/>
+      <c r="I13" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="J13" s="24" t="s">
+      <c r="J13" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="K13" s="25"/>
-      <c r="L13" s="26"/>
-    </row>
-    <row r="14" ht="33.75" customHeight="1">
+      <c r="K13" s="27"/>
+      <c r="L13" s="8"/>
+    </row>
+    <row r="14" spans="1:15" s="17" customFormat="1" ht="67.650000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="32"/>
-    </row>
-    <row r="15" ht="33.75" customHeight="1">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="9"/>
+    </row>
+    <row r="15" spans="1:15" s="17" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="32"/>
-    </row>
-    <row r="16" ht="34.5" customHeight="1">
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15" s="9"/>
+    </row>
+    <row r="16" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="7"/>
-    </row>
-    <row r="17" ht="34.5" customHeight="1">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="48" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="O16" s="51"/>
+    </row>
+    <row r="17" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="15"/>
-    </row>
-    <row r="18" ht="33.75" customHeight="1">
-      <c r="A18" s="33"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="26"/>
-    </row>
-    <row r="19" ht="33.75" customHeight="1">
-      <c r="A19" s="33"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="26"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="34"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-    </row>
-    <row r="21" ht="21.75" customHeight="1">
-      <c r="A21" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="42"/>
+      <c r="I17" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="42"/>
+      <c r="I18" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" s="8"/>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="14">
+        <v>5</v>
+      </c>
+      <c r="E19" s="14">
+        <v>4</v>
+      </c>
+      <c r="F19" s="14">
+        <v>3</v>
+      </c>
+      <c r="G19" s="45">
+        <v>2</v>
+      </c>
+      <c r="H19" s="42"/>
+      <c r="I19" s="14">
+        <v>1</v>
+      </c>
+      <c r="J19" s="15"/>
+      <c r="L19" s="8"/>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="11"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="51"/>
+    </row>
+    <row r="21" spans="1:12" s="51" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="49"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="35" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21"/>
+    </row>
+    <row r="22" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="H22" s="25"/>
-      <c r="I22" s="36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+    </row>
+    <row r="23" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="25"/>
-      <c r="I23" s="38" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="D24" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="E24" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="F24" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="G24" s="41">
-        <v>2.0</v>
-      </c>
-      <c r="H24" s="25"/>
-      <c r="I24" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="J24" s="42"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
+      <c r="C23" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="16"/>
+      <c r="H23" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
-      <c r="C25" s="43"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="42"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="1"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="47"/>
+    </row>
+    <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
+      <c r="C26" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="1"/>
+      <c r="H26" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="43"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="42"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
+      <c r="C27" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="1"/>
+      <c r="H27" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="34"/>
+      <c r="J27" s="34"/>
+    </row>
+    <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
-      <c r="C28" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" s="43"/>
-      <c r="H28" s="44" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
+    </row>
+    <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="1"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
+    </row>
+    <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="F31" s="1"/>
-      <c r="H31" s="43" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
+    </row>
+    <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="F32" s="1"/>
-      <c r="H32" s="43" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
+    </row>
+    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="F33" s="1"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
+    </row>
+    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="25">
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="D16:I16"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="J13:K13"/>
     <mergeCell ref="B2:B6"/>
@@ -1138,42 +1306,10 @@
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="E13:F13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:F15"/>
-    <mergeCell ref="G14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:K15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:F17"/>
-    <mergeCell ref="G16:H17"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="J16:K17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:F19"/>
-    <mergeCell ref="G18:H19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="J18:K19"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="H28:J28"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup fitToHeight="0" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/database/controller_excel/FO-DSP-TI-02 Reporte de auditoria a herramientas TI Rev.00.xlsx
+++ b/database/controller_excel/FO-DSP-TI-02 Reporte de auditoria a herramientas TI Rev.00.xlsx
@@ -462,7 +462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -476,7 +476,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -522,6 +521,49 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -539,55 +581,20 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -867,78 +874,78 @@
     </row>
     <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="31" t="s">
+      <c r="B2" s="44"/>
+      <c r="C2" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="27"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="43"/>
       <c r="K2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="25"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="41"/>
       <c r="K3" s="5" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="37"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="52"/>
       <c r="K4" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="38" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="25"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="41"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="37"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="52"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
@@ -955,12 +962,12 @@
       <c r="B8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="39"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
       <c r="J8" s="6" t="s">
         <v>6</v>
       </c>
@@ -981,17 +988,17 @@
       <c r="B10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="36"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="55"/>
       <c r="F10" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="39"/>
-      <c r="H10" s="36"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="55"/>
       <c r="J10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="7"/>
+      <c r="K10" s="56"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
@@ -1015,191 +1022,191 @@
     </row>
     <row r="13" spans="1:15" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="25"/>
-      <c r="G13" s="24" t="s">
+      <c r="F13" s="41"/>
+      <c r="G13" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="25"/>
-      <c r="I13" s="20" t="s">
+      <c r="H13" s="41"/>
+      <c r="I13" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="J13" s="26" t="s">
+      <c r="J13" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="K13" s="27"/>
-      <c r="L13" s="8"/>
-    </row>
-    <row r="14" spans="1:15" s="17" customFormat="1" ht="67.650000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K13" s="43"/>
+      <c r="L13" s="7"/>
+    </row>
+    <row r="14" spans="1:15" s="16" customFormat="1" ht="67.650000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="9"/>
-    </row>
-    <row r="15" spans="1:15" s="17" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="20"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="8"/>
+    </row>
+    <row r="15" spans="1:15" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
-      <c r="L15" s="9"/>
+      <c r="L15" s="8"/>
     </row>
     <row r="16" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
-      <c r="D16" s="48" t="s">
+      <c r="D16" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="O16" s="51"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="O16" s="25"/>
     </row>
     <row r="17" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="42"/>
-      <c r="I17" s="12" t="s">
+      <c r="H17" s="33"/>
+      <c r="I17" s="11" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
+      <c r="A18" s="9"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G18" s="43" t="s">
+      <c r="G18" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="42"/>
-      <c r="I18" s="13" t="s">
+      <c r="H18" s="33"/>
+      <c r="I18" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L18" s="8"/>
+      <c r="L18" s="7"/>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="14">
+      <c r="A19" s="9"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="13">
         <v>5</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="13">
         <v>4</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="13">
         <v>3</v>
       </c>
-      <c r="G19" s="45">
+      <c r="G19" s="36">
         <v>2</v>
       </c>
-      <c r="H19" s="42"/>
-      <c r="I19" s="14">
+      <c r="H19" s="33"/>
+      <c r="I19" s="13">
         <v>1</v>
       </c>
-      <c r="J19" s="15"/>
-      <c r="L19" s="8"/>
+      <c r="J19" s="14"/>
+      <c r="L19" s="7"/>
     </row>
     <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="11"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="51"/>
-    </row>
-    <row r="21" spans="1:12" s="51" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="49"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="25"/>
+    </row>
+    <row r="21" spans="1:12" s="25" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="23"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
       <c r="H21"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
       <c r="K21"/>
     </row>
     <row r="22" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
     </row>
     <row r="23" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="40" t="s">
+      <c r="C23" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="16"/>
-      <c r="H23" s="46" t="s">
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="15"/>
+      <c r="H23" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
@@ -1215,43 +1222,43 @@
     <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
       <c r="F25" s="1"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
       <c r="F26" s="1"/>
-      <c r="H26" s="40" t="s">
+      <c r="H26" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
-      <c r="C27" s="40" t="s">
+      <c r="C27" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
       <c r="F27" s="1"/>
-      <c r="H27" s="40" t="s">
+      <c r="H27" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="I27" s="34"/>
-      <c r="J27" s="34"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
     </row>
     <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
@@ -1281,11 +1288,15 @@
     <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="C2:J4"/>
+    <mergeCell ref="C5:K6"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="H27:J27"/>
     <mergeCell ref="G17:H17"/>
@@ -1296,16 +1307,12 @@
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="H25:J25"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="H26:J26"/>
     <mergeCell ref="D16:I16"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="C2:J4"/>
-    <mergeCell ref="C5:K6"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="E13:F13"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
